--- a/SGI_Sistema-de-gestao-integrado/SGE_Sistema-de-gestao-da-energia/Registos_SGE_Plasticom/SGE-01_Contexto_Ambito_Fronteiras.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGE_Sistema-de-gestao-da-energia/Registos_SGE_Plasticom/SGE-01_Contexto_Ambito_Fronteiras.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGE_Sistema-de-gestao-da-energia\Registos_SGE_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_6AC133F1136EF7E9B00636FD56B99D7296AA0414" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_8A623AF1136EF7E9B00636FDD1DD853089AA0F41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1650,7 +1650,7 @@
     <t>FRT-02</t>
   </si>
   <si>
-    <t>Nave de injeção (IM-001 a IM-008)</t>
+    <t>Nave de injeção (IM-001 a IM-009)</t>
   </si>
   <si>
     <t>QGBT-INJ</t>
